--- a/docs/StructureDefinition-BRLocalAtendimento-1.0.xlsx
+++ b/docs/StructureDefinition-BRLocalAtendimento-1.0.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -349,7 +349,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -673,7 +673,7 @@
     <t>Physical form of the location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>.playingEntity [classCode=PLC].code</t>
@@ -773,7 +773,7 @@
     <t>Location.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -795,7 +795,7 @@
     <t>Location.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -898,7 +898,7 @@
     <t>Location.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -1238,7 +1238,7 @@
     <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="20.93359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="25.8359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1383,7 +1383,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2461,7 +2461,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>146</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>161</v>
       </c>
@@ -2999,7 +2999,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>177</v>
       </c>
@@ -5579,12 +5579,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AL40">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
